--- a/data/trans_dic/P16A10-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,46</t>
+          <t>4,03; 7,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,65</t>
+          <t>3,13; 6,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,64</t>
+          <t>4,71; 8,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,37</t>
+          <t>5,18; 8,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,92</t>
+          <t>3,7; 7,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,62</t>
+          <t>4,14; 7,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,08</t>
+          <t>5,07; 9,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,51</t>
+          <t>5,59; 8,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,62</t>
+          <t>4,31; 6,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,59</t>
+          <t>4,09; 6,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,07</t>
+          <t>5,28; 8,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,08</t>
+          <t>5,79; 8,07</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,78</t>
+          <t>4,68; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,62</t>
+          <t>3,61; 6,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,25</t>
+          <t>4,32; 7,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,6</t>
+          <t>1,55; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,08</t>
+          <t>4,03; 7,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,5</t>
+          <t>3,58; 6,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,82</t>
+          <t>3,69; 6,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,91</t>
+          <t>3,82; 5,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,9</t>
+          <t>4,68; 6,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,1</t>
+          <t>3,95; 5,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,49</t>
+          <t>4,34; 6,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,72</t>
+          <t>2,7; 4,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,14</t>
+          <t>3,9; 7,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,79</t>
+          <t>3,28; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,17</t>
+          <t>4,71; 8,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,52</t>
+          <t>4,88; 8,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,05</t>
+          <t>3,48; 6,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,29</t>
+          <t>2,4; 5,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,61</t>
+          <t>4,2; 7,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,65</t>
+          <t>1,54; 4,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,5</t>
+          <t>4,06; 6,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,41</t>
+          <t>3,26; 5,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,33</t>
+          <t>4,74; 7,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,02</t>
+          <t>3,06; 5,88</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,19</t>
+          <t>3,47; 6,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,6</t>
+          <t>4,91; 8,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,35</t>
+          <t>4,35; 7,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,89</t>
+          <t>5,16; 7,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,2</t>
+          <t>4,24; 7,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,53</t>
+          <t>3,79; 6,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,08</t>
+          <t>3,17; 6,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,24</t>
+          <t>4,21; 6,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,8</t>
+          <t>4,71; 6,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,39</t>
+          <t>4,22; 6,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,59</t>
+          <t>4,87; 6,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,27</t>
+          <t>4,69; 6,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,54; 6,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,78</t>
+          <t>5,14; 6,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,18</t>
+          <t>3,92; 6,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,04</t>
+          <t>4,57; 6,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,55</t>
+          <t>4,13; 5,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,18</t>
+          <t>4,62; 6,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,53</t>
+          <t>4,0; 5,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,88</t>
+          <t>4,84; 5,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,55</t>
+          <t>4,48; 5,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,27</t>
+          <t>5,15; 6,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,71</t>
+          <t>4,5; 5,74</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27299; 51703</t>
+          <t>27953; 52235</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23229; 46683</t>
+          <t>21930; 46057</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32605; 58310</t>
+          <t>31817; 57765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32385; 53170</t>
+          <t>32891; 54831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25284; 47632</t>
+          <t>25437; 48684</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28941; 53062</t>
+          <t>28817; 54120</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33772; 61096</t>
+          <t>34105; 62079</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38002; 57505</t>
+          <t>37765; 58537</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59058; 91403</t>
+          <t>59473; 92866</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57400; 92132</t>
+          <t>57231; 93260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71948; 108768</t>
+          <t>71110; 110260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75964; 105879</t>
+          <t>75876; 105856</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43865; 74806</t>
+          <t>44970; 74560</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36126; 67349</t>
+          <t>36755; 65231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44333; 74148</t>
+          <t>44220; 74369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21212; 54858</t>
+          <t>18500; 54506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39452; 68589</t>
+          <t>39065; 68630</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36756; 66932</t>
+          <t>36831; 65202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39080; 71155</t>
+          <t>38453; 69653</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37295; 56616</t>
+          <t>36572; 56381</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91668; 133173</t>
+          <t>90384; 131247</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81549; 124961</t>
+          <t>80790; 121573</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92540; 134137</t>
+          <t>89719; 133345</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58650; 101543</t>
+          <t>58106; 102373</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26499; 48446</t>
+          <t>26468; 50068</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25404; 51343</t>
+          <t>24790; 51045</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35620; 62032</t>
+          <t>35783; 62988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35173; 59983</t>
+          <t>34328; 59490</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23594; 48215</t>
+          <t>23813; 46519</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18683; 40980</t>
+          <t>18614; 40802</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31587; 59701</t>
+          <t>32943; 59864</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15275; 43348</t>
+          <t>14373; 42835</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56531; 88495</t>
+          <t>55269; 89573</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50426; 82924</t>
+          <t>49975; 81505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72999; 113150</t>
+          <t>73199; 112596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51146; 98516</t>
+          <t>50142; 96240</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33677; 58339</t>
+          <t>32649; 57676</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47910; 81219</t>
+          <t>46346; 77961</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40818; 68865</t>
+          <t>40754; 68453</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47578; 73091</t>
+          <t>47847; 73207</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44143; 74772</t>
+          <t>44074; 74575</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38163; 68507</t>
+          <t>39709; 69560</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33610; 63446</t>
+          <t>33135; 64345</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44118; 70046</t>
+          <t>44062; 70032</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84992; 123538</t>
+          <t>83469; 119903</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92044; 135416</t>
+          <t>93772; 136330</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85354; 126533</t>
+          <t>83627; 124990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>97444; 132928</t>
+          <t>98321; 132983</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151478; 205422</t>
+          <t>153538; 202598</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153180; 207758</t>
+          <t>155255; 211198</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173541; 230261</t>
+          <t>174520; 230470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141855; 213766</t>
+          <t>135483; 213993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>154492; 204222</t>
+          <t>154493; 207824</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>144719; 196865</t>
+          <t>146419; 199323</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>163842; 219186</t>
+          <t>163587; 222624</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>144087; 202394</t>
+          <t>146292; 203907</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>319374; 391562</t>
+          <t>322063; 393925</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>314112; 386473</t>
+          <t>312413; 388024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>353330; 434981</t>
+          <t>357015; 434160</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>317171; 406526</t>
+          <t>320204; 408796</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A10-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,54</t>
+          <t>4,09; 7,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,56</t>
+          <t>3,38; 6,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,56</t>
+          <t>4,85; 8,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,63</t>
+          <t>5,31; 8,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,07</t>
+          <t>3,74; 7,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,78</t>
+          <t>3,89; 7,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,23</t>
+          <t>4,91; 9,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,66</t>
+          <t>5,6; 8,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,72</t>
+          <t>4,38; 6,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 6,67</t>
+          <t>4,17; 6,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,18</t>
+          <t>5,24; 7,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,07</t>
+          <t>5,86; 8,2</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,75</t>
+          <t>4,57; 7,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,41</t>
+          <t>3,68; 6,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,27</t>
+          <t>4,41; 7,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,57</t>
+          <t>3,07; 5,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,09</t>
+          <t>3,99; 7,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,34</t>
+          <t>3,52; 6,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,68</t>
+          <t>3,78; 6,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,89</t>
+          <t>3,73; 5,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,8</t>
+          <t>4,71; 6,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,94</t>
+          <t>3,89; 5,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,46</t>
+          <t>4,42; 6,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,76</t>
+          <t>3,65; 5,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,38</t>
+          <t>3,78; 7,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,75</t>
+          <t>3,37; 6,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,29</t>
+          <t>4,74; 8,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,45</t>
+          <t>4,86; 8,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,8</t>
+          <t>3,5; 6,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,26</t>
+          <t>2,37; 5,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,63</t>
+          <t>4,06; 7,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,59</t>
+          <t>3,3; 5,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,57</t>
+          <t>4,03; 6,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,32</t>
+          <t>3,06; 5,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,29</t>
+          <t>4,76; 7,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,88</t>
+          <t>4,48; 6,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,12</t>
+          <t>3,51; 5,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,26</t>
+          <t>4,96; 8,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,3</t>
+          <t>4,4; 7,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,9</t>
+          <t>5,02; 7,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,18</t>
+          <t>4,18; 7,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,63</t>
+          <t>3,8; 6,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,16</t>
+          <t>3,25; 6,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,42</t>
+          <t>4,67; 6,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,05</t>
+          <t>4,2; 6,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,84</t>
+          <t>4,75; 6,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,31</t>
+          <t>4,19; 6,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,59</t>
+          <t>5,15; 6,85</t>
         </is>
       </c>
     </row>
@@ -1224,27 +1224,27 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>5,39%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,19</t>
+          <t>4,7; 6,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,18</t>
+          <t>4,51; 6,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,79</t>
+          <t>5,19; 6,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,19</t>
+          <t>5,11; 6,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,15</t>
+          <t>4,6; 6,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,62</t>
+          <t>4,11; 5,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,28</t>
+          <t>4,61; 6,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,58</t>
+          <t>4,8; 5,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,92</t>
+          <t>4,8; 5,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,57</t>
+          <t>4,51; 5,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,26</t>
+          <t>5,16; 6,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,74</t>
+          <t>5,1; 6,05</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42497</t>
+          <t>47065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46957</t>
+          <t>50729</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>97794</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27953; 52235</t>
+          <t>28340; 51744</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21930; 46057</t>
+          <t>23729; 46670</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31817; 57765</t>
+          <t>32729; 57158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32891; 54831</t>
+          <t>36682; 60748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25437; 48684</t>
+          <t>25746; 50412</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28817; 54120</t>
+          <t>27073; 52117</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34105; 62079</t>
+          <t>33013; 60892</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37765; 58537</t>
+          <t>41073; 63071</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59473; 92866</t>
+          <t>60492; 92957</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57231; 93260</t>
+          <t>58221; 92066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71110; 110260</t>
+          <t>70594; 107367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75876; 105856</t>
+          <t>83423; 116773</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>42773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45445</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>92689</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44970; 74560</t>
+          <t>44000; 74072</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36755; 65231</t>
+          <t>37507; 66753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44220; 74369</t>
+          <t>45105; 74833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18500; 54506</t>
+          <t>32207; 54514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39065; 68630</t>
+          <t>38614; 68221</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36831; 65202</t>
+          <t>36220; 64808</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38453; 69653</t>
+          <t>39374; 70728</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36572; 56381</t>
+          <t>39879; 61687</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90384; 131247</t>
+          <t>90934; 131390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80790; 121573</t>
+          <t>79675; 120658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89719; 133345</t>
+          <t>91243; 133816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58106; 102373</t>
+          <t>77374; 109092</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>51204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30390</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76923</t>
+          <t>86611</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26468; 50068</t>
+          <t>25633; 48938</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24790; 51045</t>
+          <t>25523; 50799</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35783; 62988</t>
+          <t>36007; 62031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34328; 59490</t>
+          <t>38988; 66119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23813; 46519</t>
+          <t>23924; 46731</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18614; 40802</t>
+          <t>18390; 39355</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32943; 59864</t>
+          <t>31905; 60081</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14373; 42835</t>
+          <t>26779; 45818</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55269; 89573</t>
+          <t>54954; 87921</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49975; 81505</t>
+          <t>46848; 83185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73199; 112596</t>
+          <t>73598; 111305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50142; 96240</t>
+          <t>72224; 105703</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>63191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56738</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>115818</t>
+          <t>125985</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32649; 57676</t>
+          <t>33080; 56460</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46346; 77961</t>
+          <t>46781; 78877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40754; 68453</t>
+          <t>41229; 68820</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47847; 73207</t>
+          <t>49749; 76475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44074; 74575</t>
+          <t>43364; 72933</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39709; 69560</t>
+          <t>39908; 69418</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33135; 64345</t>
+          <t>33892; 64213</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44062; 70032</t>
+          <t>52122; 74869</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83469; 119903</t>
+          <t>83170; 121433</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93772; 136330</t>
+          <t>94687; 137975</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83627; 124990</t>
+          <t>82978; 124435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>98321; 132983</t>
+          <t>108544; 144292</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>153538; 202598</t>
+          <t>153862; 202443</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>155255; 211198</t>
+          <t>154266; 214229</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>174520; 230470</t>
+          <t>176028; 232086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135483; 213993</t>
+          <t>180299; 230228</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>154493; 207824</t>
+          <t>155486; 205837</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>146419; 199323</t>
+          <t>145695; 196463</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>163587; 222624</t>
+          <t>163437; 222554</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>146292; 203907</t>
+          <t>179190; 222350</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>322063; 393925</t>
+          <t>319303; 393067</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312413; 388024</t>
+          <t>314378; 386052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>357015; 434160</t>
+          <t>358205; 438331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>320204; 408796</t>
+          <t>370759; 439152</t>
         </is>
       </c>
     </row>
